--- a/Result/profitability/2428.xlsx
+++ b/Result/profitability/2428.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>2.525</v>
+        <v>2.8225</v>
       </c>
       <c r="N2" t="n">
-        <v>36.05375</v>
+        <v>35.78875000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>2.225</v>
+        <v>2.50125</v>
       </c>
       <c r="N3" t="n">
-        <v>34.4225</v>
+        <v>34.47</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9575</v>
+        <v>2.25375</v>
       </c>
       <c r="N4" t="n">
-        <v>32.795</v>
+        <v>32.58875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.625</v>
+        <v>2.01</v>
       </c>
       <c r="N5" t="n">
-        <v>31.42</v>
+        <v>30.8875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.39625</v>
+        <v>1.66375</v>
       </c>
       <c r="N6" t="n">
-        <v>29.17375</v>
+        <v>28.80625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1225</v>
+        <v>1.375</v>
       </c>
       <c r="N7" t="n">
-        <v>27.6675</v>
+        <v>27.47</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01875</v>
+        <v>1.41</v>
       </c>
       <c r="N8" t="n">
-        <v>27.0325</v>
+        <v>27.47625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9924999999999999</v>
+        <v>0.9925</v>
       </c>
       <c r="N11" t="n">
         <v>29.915</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2698</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1686</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>667</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>292</v>
+      </c>
+      <c r="J75" t="n">
+        <v>959</v>
+      </c>
+      <c r="K75" t="n">
+        <v>684</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.17375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.5975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.416289592760181</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.550000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1045039740947897</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.36283185840708</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.259999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1019626615605552</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
